--- a/2_secuencia_accion/1_formatos_asesoria_asistencia/asistencia.xlsx
+++ b/2_secuencia_accion/1_formatos_asesoria_asistencia/asistencia.xlsx
@@ -1,73 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marco\Documentos\investigacion\investigacion_en_asesoria\2_secuencia_accion\1_formatos_asesoria_asistencia\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018FAC55-53B0-4A10-BCD5-A93FF65F8F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>Correo</t>
-  </si>
-  <si>
-    <t>Programa</t>
-  </si>
-  <si>
-    <t>Dificultad/Solicitud</t>
-  </si>
-  <si>
-    <t>marco</t>
-  </si>
-  <si>
-    <t>marco julio cañas campillo</t>
-  </si>
-  <si>
-    <t>marco.canas@udea.edu.co</t>
-  </si>
-  <si>
-    <t>dirección de regionalización</t>
-  </si>
-  <si>
-    <t>controlar mi reacción a los momentos de la vida</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -86,12 +46,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -161,14 +120,6 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -456,49 +407,154 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="31.21875" customWidth="1"/>
-    <col min="3" max="3" width="31.109375" customWidth="1"/>
-    <col min="4" max="4" width="44.33203125" customWidth="1"/>
-    <col min="5" max="5" width="48.6640625" customWidth="1"/>
-    <col min="6" max="6" width="41.33203125" customWidth="1"/>
+    <col width="31.21875" customWidth="1" min="2" max="2"/>
+    <col width="31.109375" customWidth="1" min="3" max="3"/>
+    <col width="44.33203125" customWidth="1" min="4" max="4"/>
+    <col width="48.6640625" customWidth="1" min="5" max="5"/>
+    <col width="41.33203125" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Correo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Programa</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Dificultad/Solicitud</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>marco</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>marco julio cañas campillo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>marco.canas@udea.edu.co</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>dirección de regionalización</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>controlar mi reacción a los momentos de la vida</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>manuel medina</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>manuel.medinag@udea.edu.co</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lic matemática </t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>representaciones de una función cuadrática</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>camilo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>juan camilo guerra mercado</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>camilo.jmercado@udea.edu.co</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>lic matemáticas</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>representaciones analíticas de la función cuadrática</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>fernanda</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>luisa fernanda gonzalez basilio</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>luisaf.gonzalez1@udea.edu.co</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>lic matemáticas</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>modelación en estadística</t>
+        </is>
       </c>
     </row>
   </sheetData>
